--- a/public/excel-template.xlsx
+++ b/public/excel-template.xlsx
@@ -4,13 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12860" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Column1</t>
   </si>
@@ -937,21 +935,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:D2" insertRow="1" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D2" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Column1"/>
-    <tableColumn id="2" name="Column2"/>
-    <tableColumn id="3" name="Column3"/>
-    <tableColumn id="4" name="Column4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D2" insertRow="1" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D2" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:D4" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D4" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Column2"/>
@@ -1212,11 +1197,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
-  <sheetData/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>222</v>
+      </c>
+      <c r="B2">
+        <v>333</v>
+      </c>
+      <c r="C2">
+        <v>444</v>
+      </c>
+      <c r="D2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>222</v>
+      </c>
+      <c r="B3">
+        <v>333</v>
+      </c>
+      <c r="C3">
+        <v>444</v>
+      </c>
+      <c r="D3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>222</v>
+      </c>
+      <c r="B4">
+        <v>333</v>
+      </c>
+      <c r="C4">
+        <v>444</v>
+      </c>
+      <c r="D4">
+        <v>555</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1229,62 +1274,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>